--- a/AAII_Financials/Quarterly/HKXCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HKXCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="92">
   <si>
     <t>HKXCY</t>
   </si>
@@ -656,80 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +776,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +823,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +983,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1095,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1113,8 +1140,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1157,8 +1187,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1208,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1219,8 +1253,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,8 +1300,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,8 +1347,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1351,8 +1394,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1488,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1483,8 +1535,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,8 +1582,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1770,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,8 +1817,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1791,8 +1864,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1911,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1879,57 +1958,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,140 +2050,150 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2437400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2486400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21752800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2352900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18172400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1790800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29314400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1707700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17365200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16015000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17739000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1738200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22125100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23721700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18940800</v>
+      </c>
+      <c r="E42" s="3">
         <v>704100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17703300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13829300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13595900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1770500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5340100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11977100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8991400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2849100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12012300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2515800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9552000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2293400</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6052100</v>
+        <v>7823000</v>
       </c>
       <c r="E43" s="3">
+        <v>6103700</v>
+      </c>
+      <c r="F43" s="3">
         <v>8752500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4829100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6287600</v>
       </c>
-      <c r="H43" s="3">
-        <v>4488800</v>
-      </c>
       <c r="I43" s="3">
+        <v>4521900</v>
+      </c>
+      <c r="J43" s="3">
         <v>6778700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2069700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3861800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3029000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3884800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1420300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2792500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1947600</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2140,228 +2236,246 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>40167800</v>
+        <v>19694700</v>
       </c>
       <c r="E45" s="3">
+        <v>40116200</v>
+      </c>
+      <c r="F45" s="3">
         <v>6840200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9288500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7037100</v>
       </c>
-      <c r="H45" s="3">
-        <v>21964700</v>
-      </c>
       <c r="I45" s="3">
+        <v>21931600</v>
+      </c>
+      <c r="J45" s="3">
         <v>12017100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13064600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7243700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18586500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6930700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19563000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8779000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21092700</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68911300</v>
+      </c>
+      <c r="E46" s="3">
         <v>70400000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55048700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50099400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45093100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45522400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>53450400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46832500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37462100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40479700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40566800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42459000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43248600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49055300</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1149400</v>
+      </c>
+      <c r="E47" s="3">
         <v>384300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>979000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>951300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>913900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>334700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6177100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>709000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3117500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>335500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>341600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>337300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2258000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>165100</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>942900</v>
+      </c>
+      <c r="E48" s="3">
         <v>636700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>540200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>532500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>350100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>344800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>347600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>352400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>376300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>388800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>369200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>383100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>399700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>416000</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2581800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2561600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2550900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2540000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2537000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2524000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2504700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2486200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2475000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2467900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2447100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2435300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2430500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2432600</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
         <v>633000</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>2400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>404500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>2400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>2700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>2700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73587200</v>
+      </c>
+      <c r="E54" s="3">
         <v>74616800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>59219200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54124200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48897400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49131500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>62482900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>50382000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43436600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43674500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43735100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45619200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48343700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>52075800</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2746,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8376700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6301600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6788800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5039600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4166500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4648700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9455800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3360200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2691800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3354100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3863800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2537500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2326900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2085600</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E58" s="3">
         <v>71600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>70900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>70700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>83500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>82700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>80900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>83300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>83500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>86800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>88300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>91000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>93200</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57084600</v>
+      </c>
+      <c r="E59" s="3">
         <v>60119200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>44962200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41395000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>37555800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36919700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>46027600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39781700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33918500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33145200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>33123900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35979300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39287000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42969200</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65503900</v>
+      </c>
+      <c r="E60" s="3">
         <v>66664000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51821900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46505400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41805800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41779900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55525300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43222800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36693600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36676500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>37074500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38605100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>41704800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45265400</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E61" s="3">
         <v>88900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>94600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>90800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>136000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>142100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>191000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>157400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>173100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>179100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>174600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>182000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>188300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>193500</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E62" s="3">
         <v>100500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>75300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>15800</v>
       </c>
       <c r="H62" s="3">
         <v>15800</v>
       </c>
       <c r="I62" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J62" s="3">
         <v>16000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>65814900</v>
+      </c>
+      <c r="E66" s="3">
         <v>67071400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52191900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46805500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>42146000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>42127100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55902800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43566200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37053100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37044100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37434600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38974300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42085100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45650700</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3783000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3510400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2959300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3272300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2728200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3005000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2520800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2809200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2397900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2655100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2318500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2665000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2289400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2466600</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7734700</v>
+      </c>
+      <c r="E76" s="3">
         <v>7470600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6956100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7249700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6677300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6933000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6511000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6750300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6321900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6572600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6242500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6591000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6207500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6377600</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3703,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3607,8 +3802,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,8 +4103,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3933,8 +4150,11 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4171,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3995,8 +4216,11 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,8 +4310,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4127,8 +4357,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,8 +4564,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4365,8 +4611,11 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,8 +4658,11 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4451,6 +4703,9 @@
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
